--- a/Diary/考研/前期规划/大三下结合课表每日安排.xlsx
+++ b/Diary/考研/前期规划/大三下结合课表每日安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\考研\前期规划\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BD2948-63D4-48E0-A107-AB39D0ADA7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0799248-0056-479E-B059-A5C0923F11AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>周一</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -159,6 +159,22 @@
   </si>
   <si>
     <t>考研学习规划</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>专业课 &amp;课内课程学习</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -169,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,8 +214,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,8 +241,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -237,32 +290,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -294,26 +321,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -321,7 +328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -338,29 +345,38 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -643,26 +659,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="1"/>
     <col min="2" max="8" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -685,104 +703,114 @@
       <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="10"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="15" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -798,17 +826,19 @@
       <c r="E7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -824,19 +854,21 @@
       <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="11"/>
       <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="10"/>
@@ -844,19 +876,29 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="10"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -866,7 +908,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -876,7 +918,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -886,7 +928,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -896,7 +938,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -906,7 +948,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -917,11 +959,12 @@
       <c r="H16" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G10:H10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/考研/前期规划/大三下结合课表每日安排.xlsx
+++ b/Diary/考研/前期规划/大三下结合课表每日安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\考研\前期规划\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0799248-0056-479E-B059-A5C0923F11AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25399E24-9258-46E2-96EE-9EEA0B066905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
   <si>
     <t>周一</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -345,37 +345,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -667,18 +667,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -703,112 +703,116 @@
       <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
@@ -826,17 +830,17 @@
       <c r="E7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -854,49 +858,49 @@
       <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="13"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
